--- a/assistente_administrativo/fmdt/chamada.xlsx
+++ b/assistente_administrativo/fmdt/chamada.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="55">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">Emanuelle Santos da Cruz</t>
   </si>
   <si>
+    <t xml:space="preserve">|</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gabriela Costa de Lima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|</t>
   </si>
   <si>
     <t xml:space="preserve">Guilherme Expedito Ferigatti</t>
@@ -319,12 +319,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="12.58984375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -340,8 +342,14 @@
       <c r="D1" s="3" t="n">
         <v>45743</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E1" s="3" t="n">
+        <v>45750</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -354,8 +362,14 @@
       <c r="D2" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -368,8 +382,14 @@
       <c r="D3" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -382,8 +402,14 @@
       <c r="D4" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E4" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -396,8 +422,14 @@
       <c r="D5" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -410,8 +442,14 @@
       <c r="D6" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E6" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -424,22 +462,34 @@
       <c r="D7" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -452,8 +502,14 @@
       <c r="D9" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -466,8 +522,14 @@
       <c r="D10" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -475,13 +537,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -492,10 +560,16 @@
         <v>2</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -508,8 +582,14 @@
       <c r="D13" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E13" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -522,8 +602,14 @@
       <c r="D14" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E14" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -536,8 +622,14 @@
       <c r="D15" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E15" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -550,8 +642,14 @@
       <c r="D16" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
@@ -564,8 +662,14 @@
       <c r="D17" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
@@ -578,8 +682,14 @@
       <c r="D18" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
@@ -592,8 +702,14 @@
       <c r="D19" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
@@ -606,8 +722,14 @@
       <c r="D20" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -620,8 +742,14 @@
       <c r="D21" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
@@ -634,8 +762,14 @@
       <c r="D22" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -648,8 +782,14 @@
       <c r="D23" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
@@ -662,8 +802,14 @@
       <c r="D24" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
@@ -676,8 +822,14 @@
       <c r="D25" s="0" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>27</v>
       </c>
@@ -688,6 +840,12 @@
         <v>2</v>
       </c>
       <c r="D26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -708,7 +866,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.58984375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>
@@ -793,7 +951,7 @@
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>36</v>

--- a/assistente_administrativo/fmdt/chamada.xlsx
+++ b/assistente_administrativo/fmdt/chamada.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="55">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -319,14 +319,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -348,6 +348,9 @@
       <c r="F1" s="3" t="n">
         <v>45757</v>
       </c>
+      <c r="G1" s="3" t="n">
+        <v>45764</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -368,6 +371,9 @@
       <c r="F2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -388,6 +394,9 @@
       <c r="F3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -408,6 +417,9 @@
       <c r="F4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -428,6 +440,9 @@
       <c r="F5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -448,6 +463,9 @@
       <c r="F6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -468,6 +486,9 @@
       <c r="F7" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="G7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -488,6 +509,9 @@
       <c r="F8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -508,6 +532,9 @@
       <c r="F9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -528,6 +555,9 @@
       <c r="F10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -548,6 +578,9 @@
       <c r="F11" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="G11" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -568,6 +601,9 @@
       <c r="F12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -588,6 +624,9 @@
       <c r="F13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G13" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -608,6 +647,9 @@
       <c r="F14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -628,6 +670,9 @@
       <c r="F15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -648,6 +693,9 @@
       <c r="F16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -668,6 +716,9 @@
       <c r="F17" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G17" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -688,6 +739,9 @@
       <c r="F18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -708,6 +762,9 @@
       <c r="F19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -728,6 +785,9 @@
       <c r="F20" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G20" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -748,6 +808,9 @@
       <c r="F21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -768,6 +831,9 @@
       <c r="F22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -788,6 +854,9 @@
       <c r="F23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -808,6 +877,9 @@
       <c r="F24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -828,6 +900,9 @@
       <c r="F25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="G25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -846,6 +921,9 @@
         <v>2</v>
       </c>
       <c r="F26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -866,7 +944,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>

--- a/assistente_administrativo/fmdt/chamada.xlsx
+++ b/assistente_administrativo/fmdt/chamada.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="55">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -319,14 +319,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.85"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -351,6 +351,9 @@
       <c r="G1" s="3" t="n">
         <v>45764</v>
       </c>
+      <c r="H1" s="3" t="n">
+        <v>45771</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -374,6 +377,9 @@
       <c r="G2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -397,6 +403,9 @@
       <c r="G3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -420,6 +429,9 @@
       <c r="G4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -443,6 +455,9 @@
       <c r="G5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -466,6 +481,9 @@
       <c r="G6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -489,6 +507,9 @@
       <c r="G7" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -512,6 +533,9 @@
       <c r="G8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -535,6 +559,9 @@
       <c r="G9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -558,6 +585,9 @@
       <c r="G10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -581,6 +611,9 @@
       <c r="G11" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="H11" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -604,6 +637,9 @@
       <c r="G12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -627,6 +663,9 @@
       <c r="G13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H13" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -650,6 +689,9 @@
       <c r="G14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -673,6 +715,9 @@
       <c r="G15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -696,6 +741,9 @@
       <c r="G16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -719,6 +767,9 @@
       <c r="G17" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H17" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -742,6 +793,9 @@
       <c r="G18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -765,6 +819,9 @@
       <c r="G19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -788,6 +845,9 @@
       <c r="G20" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="H20" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -811,6 +871,9 @@
       <c r="G21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -834,6 +897,9 @@
       <c r="G22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -857,6 +923,9 @@
       <c r="G23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -880,6 +949,9 @@
       <c r="G24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -903,6 +975,9 @@
       <c r="G25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="H25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -924,6 +999,9 @@
         <v>2</v>
       </c>
       <c r="G26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -944,7 +1022,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>

--- a/assistente_administrativo/fmdt/chamada.xlsx
+++ b/assistente_administrativo/fmdt/chamada.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="55">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -319,14 +319,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -354,6 +355,9 @@
       <c r="H1" s="3" t="n">
         <v>45771</v>
       </c>
+      <c r="I1" s="3" t="n">
+        <v>45785</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -380,6 +384,9 @@
       <c r="H2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -406,6 +413,9 @@
       <c r="H3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -432,6 +442,9 @@
       <c r="H4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -458,6 +471,9 @@
       <c r="H5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -484,6 +500,9 @@
       <c r="H6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -510,6 +529,9 @@
       <c r="H7" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -536,6 +558,9 @@
       <c r="H8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -562,6 +587,9 @@
       <c r="H9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -588,6 +616,9 @@
       <c r="H10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -614,6 +645,9 @@
       <c r="H11" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I11" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -640,6 +674,9 @@
       <c r="H12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -666,6 +703,9 @@
       <c r="H13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I13" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -692,6 +732,9 @@
       <c r="H14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -718,6 +761,9 @@
       <c r="H15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -744,6 +790,9 @@
       <c r="H16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -770,6 +819,9 @@
       <c r="H17" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I17" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -796,6 +848,9 @@
       <c r="H18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -822,6 +877,9 @@
       <c r="H19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -848,6 +906,9 @@
       <c r="H20" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I20" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -874,6 +935,9 @@
       <c r="H21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -900,6 +964,9 @@
       <c r="H22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -926,6 +993,9 @@
       <c r="H23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -952,6 +1022,9 @@
       <c r="H24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -978,6 +1051,9 @@
       <c r="H25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="I25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -1002,6 +1078,9 @@
         <v>2</v>
       </c>
       <c r="H26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1022,7 +1101,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6953125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>

--- a/assistente_administrativo/fmdt/chamada.xlsx
+++ b/assistente_administrativo/fmdt/chamada.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Chamada" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Usuários" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Custos" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="80">
   <si>
     <t xml:space="preserve">Nome</t>
   </si>
@@ -186,17 +187,93 @@
   </si>
   <si>
     <t xml:space="preserve">tamires.mendes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabela de custos de ingredientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pastel de Carne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pastel de Frango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidade Kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azeitona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cebola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coloral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Óleo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pimenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presunto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custo total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pastel de Queijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pastel de Pizza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orégano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="d/mmm"/>
+    <numFmt numFmtId="166" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -234,13 +311,27 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EA6B"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -277,7 +368,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -302,6 +393,26 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -311,6 +422,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD4EA6B"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -319,15 +490,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="6.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.2"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -358,6 +530,9 @@
       <c r="I1" s="3" t="n">
         <v>45785</v>
       </c>
+      <c r="J1" s="3" t="n">
+        <v>45792</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -387,6 +562,9 @@
       <c r="I2" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J2" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -416,6 +594,9 @@
       <c r="I3" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J3" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -445,6 +626,9 @@
       <c r="I4" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J4" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -474,6 +658,9 @@
       <c r="I5" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J5" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -503,6 +690,9 @@
       <c r="I6" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J6" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
@@ -532,6 +722,9 @@
       <c r="I7" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J7" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
@@ -561,6 +754,9 @@
       <c r="I8" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J8" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
@@ -590,6 +786,9 @@
       <c r="I9" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J9" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
@@ -619,6 +818,9 @@
       <c r="I10" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J10" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -648,6 +850,9 @@
       <c r="I11" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J11" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
@@ -677,6 +882,9 @@
       <c r="I12" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J12" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
@@ -706,6 +914,9 @@
       <c r="I13" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J13" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
@@ -735,6 +946,9 @@
       <c r="I14" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J14" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
@@ -764,6 +978,9 @@
       <c r="I15" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J15" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -793,6 +1010,9 @@
       <c r="I16" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J16" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -822,6 +1042,9 @@
       <c r="I17" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="J17" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -851,6 +1074,9 @@
       <c r="I18" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J18" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
@@ -880,6 +1106,9 @@
       <c r="I19" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J19" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
@@ -909,6 +1138,9 @@
       <c r="I20" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J20" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
@@ -938,6 +1170,9 @@
       <c r="I21" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J21" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -967,6 +1202,9 @@
       <c r="I22" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J22" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
@@ -996,6 +1234,9 @@
       <c r="I23" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J23" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
@@ -1025,6 +1266,9 @@
       <c r="I24" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J24" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
@@ -1054,6 +1298,9 @@
       <c r="I25" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="J25" s="0" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
@@ -1081,6 +1328,9 @@
         <v>2</v>
       </c>
       <c r="I26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="0" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1101,7 +1351,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="12.6953125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="15.71"/>
@@ -1402,4 +1652,473 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6.43"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="I1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="J12" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="I14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E17" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E19" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="I20" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I22" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="I14:K14"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>